--- a/output/laminas_provinciales/prov_i_ingr_median_a_2022_valparaiso.xlsx
+++ b/output/laminas_provinciales/prov_i_ingr_median_a_2022_valparaiso.xlsx
@@ -353,7 +353,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -408,7 +408,7 @@
         <v>547410.5</v>
       </c>
       <c r="G2">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3">
@@ -426,7 +426,7 @@
         <v>697990</v>
       </c>
       <c r="G3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4">
@@ -444,7 +444,7 @@
         <v>625000</v>
       </c>
       <c r="G4">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5">
@@ -462,7 +462,7 @@
         <v>608700</v>
       </c>
       <c r="G5">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6">
@@ -480,7 +480,7 @@
         <v>707740</v>
       </c>
       <c r="G6">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7">
@@ -498,7 +498,7 @@
         <v>659740</v>
       </c>
       <c r="G7">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         <v>596660</v>
       </c>
       <c r="G8">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
@@ -534,7 +534,7 @@
         <v>728650</v>
       </c>
       <c r="G9">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10">
@@ -552,13 +552,13 @@
         <v>661953</v>
       </c>
       <c r="G10">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Quillota</t>
+          <t>Promedio Regional</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -567,16 +567,25 @@
         </is>
       </c>
       <c r="C11">
-        <v>599435</v>
+        <v>623340</v>
+      </c>
+      <c r="D11">
+        <v>560430</v>
+      </c>
+      <c r="E11">
+        <v>62910</v>
+      </c>
+      <c r="F11">
+        <v>11.22530913762647</v>
       </c>
       <c r="G11">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Quillota</t>
+          <t>Promedio Regional</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -585,16 +594,25 @@
         </is>
       </c>
       <c r="C12">
-        <v>804006</v>
+        <v>766250</v>
+      </c>
+      <c r="D12">
+        <v>658860</v>
+      </c>
+      <c r="E12">
+        <v>107390</v>
+      </c>
+      <c r="F12">
+        <v>16.29936557083447</v>
       </c>
       <c r="G12">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Quillota</t>
+          <t>Promedio Regional</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -603,16 +621,25 @@
         </is>
       </c>
       <c r="C13">
-        <v>704000</v>
+        <v>700000</v>
+      </c>
+      <c r="D13">
+        <v>612521</v>
+      </c>
+      <c r="E13">
+        <v>87479</v>
+      </c>
+      <c r="F13">
+        <v>14.28179605270676</v>
       </c>
       <c r="G13">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Marga Marga</t>
+          <t>Quillota</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -621,16 +648,16 @@
         </is>
       </c>
       <c r="C14">
-        <v>632310</v>
+        <v>599435</v>
       </c>
       <c r="G14">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Marga Marga</t>
+          <t>Quillota</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -639,16 +666,16 @@
         </is>
       </c>
       <c r="C15">
-        <v>772170</v>
+        <v>804006</v>
       </c>
       <c r="G15">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Marga Marga</t>
+          <t>Quillota</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -657,16 +684,16 @@
         </is>
       </c>
       <c r="C16">
-        <v>706110</v>
+        <v>704000</v>
       </c>
       <c r="G16">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Marga Marga</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -675,16 +702,16 @@
         </is>
       </c>
       <c r="C17">
-        <v>641347.5</v>
+        <v>632310</v>
       </c>
       <c r="G17">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Marga Marga</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -693,16 +720,16 @@
         </is>
       </c>
       <c r="C18">
-        <v>762500</v>
+        <v>772170</v>
       </c>
       <c r="G18">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Marga Marga</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -711,16 +738,16 @@
         </is>
       </c>
       <c r="C19">
-        <v>708330</v>
+        <v>706110</v>
       </c>
       <c r="G19">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -729,16 +756,16 @@
         </is>
       </c>
       <c r="C20">
-        <v>624090</v>
+        <v>641347.5</v>
       </c>
       <c r="G20">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -747,16 +774,16 @@
         </is>
       </c>
       <c r="C21">
-        <v>919638</v>
+        <v>762500</v>
       </c>
       <c r="G21">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -765,16 +792,16 @@
         </is>
       </c>
       <c r="C22">
-        <v>777105</v>
+        <v>708330</v>
       </c>
       <c r="G22">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Isla de Pascua</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -783,16 +810,16 @@
         </is>
       </c>
       <c r="C23">
-        <v>870620</v>
+        <v>624090</v>
       </c>
       <c r="G23">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Isla de Pascua</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -801,27 +828,81 @@
         </is>
       </c>
       <c r="C24">
-        <v>880400</v>
+        <v>919638</v>
       </c>
       <c r="G24">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>Los Andes</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C25">
+        <v>777105</v>
+      </c>
+      <c r="G25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
           <t>Isla de Pascua</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="C26">
+        <v>870620</v>
+      </c>
+      <c r="G26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Isla de Pascua</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="C27">
+        <v>880400</v>
+      </c>
+      <c r="G27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Isla de Pascua</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="C25">
+      <c r="C28">
         <v>877160</v>
       </c>
-      <c r="G25">
+      <c r="G28">
         <v>1</v>
       </c>
     </row>
@@ -924,7 +1005,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D28"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1381,6 +1462,60 @@
         <v>0</v>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Promedio Regional</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="C26">
+        <v>700000</v>
+      </c>
+      <c r="D26" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Promedio Regional</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="C27">
+        <v>794428</v>
+      </c>
+      <c r="D27" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Promedio Regional</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="C28">
+        <v>856320</v>
+      </c>
+      <c r="D28" t="b">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/output/laminas_provinciales/prov_i_ingr_median_a_2022_valparaiso.xlsx
+++ b/output/laminas_provinciales/prov_i_ingr_median_a_2022_valparaiso.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
   <si>
     <t xml:space="preserve">Provincia</t>
   </si>
@@ -86,7 +86,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-27 22:14</t>
+    <t xml:space="preserve">2026-08-19 13:49</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -98,13 +98,19 @@
     <t xml:space="preserve">Imagen asociada</t>
   </si>
   <si>
-    <t xml:space="preserve"/>
+    <t xml:space="preserve">prov_i_ingr_median_a_2022_valparaiso.png</t>
   </si>
   <si>
     <t xml:space="preserve">Indicador</t>
   </si>
   <si>
+    <t xml:space="preserve">Mediana ingreso de asalariados dependientes</t>
+  </si>
+  <si>
     <t xml:space="preserve">Unidad territorial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Region de Valparaíso</t>
   </si>
   <si>
     <t xml:space="preserve">Año</t>
@@ -1049,23 +1055,23 @@
         <v>27</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -1088,7 +1094,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="2">
@@ -1169,10 +1175,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2">
@@ -1180,7 +1186,7 @@
         <v>18</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>877160</v>
@@ -1191,7 +1197,7 @@
         <v>18</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C3" s="2" t="n">
         <v>995600</v>
@@ -1202,7 +1208,7 @@
         <v>18</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C4" s="2" t="n">
         <v>1052917</v>
@@ -1213,7 +1219,7 @@
         <v>17</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C5" s="2" t="n">
         <v>777105</v>
@@ -1224,7 +1230,7 @@
         <v>17</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C6" s="2" t="n">
         <v>896030</v>
@@ -1235,7 +1241,7 @@
         <v>17</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C7" s="2" t="n">
         <v>951280</v>
@@ -1246,7 +1252,7 @@
         <v>15</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C8" s="2" t="n">
         <v>706110</v>
@@ -1257,7 +1263,7 @@
         <v>15</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C9" s="2" t="n">
         <v>800000</v>
@@ -1268,7 +1274,7 @@
         <v>15</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C10" s="2" t="n">
         <v>862813</v>
@@ -1279,7 +1285,7 @@
         <v>7</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C11" s="2" t="n">
         <v>625000</v>
@@ -1290,7 +1296,7 @@
         <v>7</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C12" s="2" t="n">
         <v>712017</v>
@@ -1301,7 +1307,7 @@
         <v>7</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C13" s="2" t="n">
         <v>763228</v>
@@ -1312,7 +1318,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C14" s="2" t="n">
         <v>704000</v>
@@ -1323,7 +1329,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C15" s="2" t="n">
         <v>800000</v>
@@ -1334,7 +1340,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C16" s="2" t="n">
         <v>868260</v>
@@ -1345,7 +1351,7 @@
         <v>11</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C17" s="2" t="n">
         <v>659740</v>
@@ -1356,7 +1362,7 @@
         <v>11</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C18" s="2" t="n">
         <v>750000</v>
@@ -1367,7 +1373,7 @@
         <v>11</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C19" s="2" t="n">
         <v>800000</v>
@@ -1378,7 +1384,7 @@
         <v>12</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C20" s="2" t="n">
         <v>661953</v>
@@ -1389,7 +1395,7 @@
         <v>12</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C21" s="2" t="n">
         <v>755848</v>
@@ -1400,7 +1406,7 @@
         <v>12</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C22" s="2" t="n">
         <v>814966</v>
@@ -1411,7 +1417,7 @@
         <v>16</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C23" s="2" t="n">
         <v>708330</v>
@@ -1422,7 +1428,7 @@
         <v>16</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C24" s="2" t="n">
         <v>802380</v>
@@ -1433,7 +1439,7 @@
         <v>16</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C25" s="2" t="n">
         <v>862500</v>
@@ -1444,7 +1450,7 @@
         <v>13</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C26" s="2" t="n">
         <v>700000</v>
@@ -1455,7 +1461,7 @@
         <v>13</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C27" s="2" t="n">
         <v>794428</v>
@@ -1466,7 +1472,7 @@
         <v>13</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C28" s="2" t="n">
         <v>856320</v>

--- a/output/laminas_provinciales/prov_i_ingr_median_a_2022_valparaiso.xlsx
+++ b/output/laminas_provinciales/prov_i_ingr_median_a_2022_valparaiso.xlsx
@@ -86,7 +86,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-19 13:49</t>
+    <t xml:space="preserve">2026-09-07 11:13</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
